--- a/template.xlsx
+++ b/template.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R39a34df09098411b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R922c7fb90f354245"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -225,7 +225,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="76">
+  <x:cellXfs count="72">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -390,18 +390,30 @@
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="200" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="179" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
@@ -412,9 +424,6 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="179" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -428,27 +437,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -654,9 +642,9 @@
   <x:cols>
     <x:col min="1" max="1" width="15" style="4" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="18" style="4" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="25" style="4" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="26" style="4" hidden="0" customWidth="1"/>
     <x:col min="4" max="6" width="15.6640625" style="4" customWidth="1"/>
-    <x:col min="7" max="7" width="32" style="4" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="34" style="4" hidden="0" customWidth="1"/>
     <x:col min="8" max="16384" width="9" style="4" customWidth="0"/>
     <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
@@ -696,113 +684,113 @@
       <x:c r="G3" s="25"/>
     </x:row>
     <x:row r="4" s="12" customFormat="1" ht="30" customHeight="1">
-      <x:c r="A4" s="56" t="s">
+      <x:c r="A4" s="62" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B4" s="56" t="s">
+      <x:c r="B4" s="62" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C4" s="56" t="s">
+      <x:c r="C4" s="62" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D4" s="56" t="s">
+      <x:c r="D4" s="62" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="E4" s="56" t="s">
+      <x:c r="E4" s="62" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="F4" s="56" t="s">
+      <x:c r="F4" s="62" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G4" s="56" t="s">
+      <x:c r="G4" s="62" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="32" customHeight="1">
-      <x:c r="A5" s="74"/>
-      <x:c r="B5" s="58"/>
-      <x:c r="C5" s="58"/>
-      <x:c r="D5" s="70"/>
-      <x:c r="E5" s="58"/>
-      <x:c r="F5" s="58"/>
-      <x:c r="G5" s="68"/>
+      <x:c r="A5" s="60"/>
+      <x:c r="B5" s="63"/>
+      <x:c r="C5" s="63"/>
+      <x:c r="D5" s="56"/>
+      <x:c r="E5" s="63"/>
+      <x:c r="F5" s="63"/>
+      <x:c r="G5" s="71"/>
     </x:row>
     <x:row r="6" ht="32" customHeight="1">
-      <x:c r="A6" s="74"/>
-      <x:c r="B6" s="58"/>
-      <x:c r="C6" s="58"/>
-      <x:c r="D6" s="70"/>
-      <x:c r="E6" s="58"/>
-      <x:c r="F6" s="58"/>
-      <x:c r="G6" s="68"/>
+      <x:c r="A6" s="60"/>
+      <x:c r="B6" s="63"/>
+      <x:c r="C6" s="63"/>
+      <x:c r="D6" s="56"/>
+      <x:c r="E6" s="63"/>
+      <x:c r="F6" s="63"/>
+      <x:c r="G6" s="71"/>
     </x:row>
     <x:row r="7" ht="32" customHeight="1">
-      <x:c r="A7" s="74"/>
-      <x:c r="B7" s="58"/>
-      <x:c r="C7" s="58"/>
-      <x:c r="D7" s="70"/>
-      <x:c r="E7" s="58"/>
-      <x:c r="F7" s="58"/>
-      <x:c r="G7" s="68"/>
+      <x:c r="A7" s="60"/>
+      <x:c r="B7" s="63"/>
+      <x:c r="C7" s="63"/>
+      <x:c r="D7" s="56"/>
+      <x:c r="E7" s="63"/>
+      <x:c r="F7" s="63"/>
+      <x:c r="G7" s="71"/>
     </x:row>
     <x:row r="8" ht="32" customHeight="1">
-      <x:c r="A8" s="74"/>
-      <x:c r="B8" s="58"/>
-      <x:c r="C8" s="58"/>
-      <x:c r="D8" s="70"/>
-      <x:c r="E8" s="58"/>
-      <x:c r="F8" s="58"/>
-      <x:c r="G8" s="68"/>
+      <x:c r="A8" s="60"/>
+      <x:c r="B8" s="63"/>
+      <x:c r="C8" s="63"/>
+      <x:c r="D8" s="56"/>
+      <x:c r="E8" s="63"/>
+      <x:c r="F8" s="63"/>
+      <x:c r="G8" s="71"/>
     </x:row>
     <x:row r="9" ht="32" customHeight="1">
-      <x:c r="A9" s="74"/>
-      <x:c r="B9" s="58"/>
-      <x:c r="C9" s="58"/>
-      <x:c r="D9" s="70"/>
-      <x:c r="E9" s="58"/>
-      <x:c r="F9" s="58"/>
-      <x:c r="G9" s="68"/>
+      <x:c r="A9" s="60"/>
+      <x:c r="B9" s="63"/>
+      <x:c r="C9" s="63"/>
+      <x:c r="D9" s="56"/>
+      <x:c r="E9" s="63"/>
+      <x:c r="F9" s="63"/>
+      <x:c r="G9" s="71"/>
     </x:row>
     <x:row r="10" ht="32" customHeight="1">
-      <x:c r="A10" s="74"/>
-      <x:c r="B10" s="58"/>
-      <x:c r="C10" s="58"/>
-      <x:c r="D10" s="70"/>
-      <x:c r="E10" s="58"/>
-      <x:c r="F10" s="58"/>
-      <x:c r="G10" s="68"/>
+      <x:c r="A10" s="60"/>
+      <x:c r="B10" s="63"/>
+      <x:c r="C10" s="63"/>
+      <x:c r="D10" s="56"/>
+      <x:c r="E10" s="63"/>
+      <x:c r="F10" s="63"/>
+      <x:c r="G10" s="71"/>
     </x:row>
     <x:row r="11" ht="32" customHeight="1">
-      <x:c r="A11" s="74"/>
-      <x:c r="B11" s="58"/>
-      <x:c r="C11" s="58"/>
-      <x:c r="D11" s="70"/>
-      <x:c r="E11" s="58"/>
-      <x:c r="F11" s="58"/>
-      <x:c r="G11" s="68"/>
+      <x:c r="A11" s="60"/>
+      <x:c r="B11" s="63"/>
+      <x:c r="C11" s="63"/>
+      <x:c r="D11" s="56"/>
+      <x:c r="E11" s="63"/>
+      <x:c r="F11" s="63"/>
+      <x:c r="G11" s="71"/>
     </x:row>
     <x:row r="12" ht="32" customHeight="1">
-      <x:c r="A12" s="74"/>
-      <x:c r="B12" s="58"/>
-      <x:c r="C12" s="58"/>
-      <x:c r="D12" s="70"/>
-      <x:c r="E12" s="58"/>
-      <x:c r="F12" s="58"/>
-      <x:c r="G12" s="68"/>
+      <x:c r="A12" s="60"/>
+      <x:c r="B12" s="63"/>
+      <x:c r="C12" s="63"/>
+      <x:c r="D12" s="56"/>
+      <x:c r="E12" s="63"/>
+      <x:c r="F12" s="63"/>
+      <x:c r="G12" s="71"/>
     </x:row>
     <x:row r="13" ht="30" customHeight="1">
-      <x:c r="A13" s="61" t="s">
+      <x:c r="A13" s="65" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B13" s="62"/>
-      <x:c r="C13" s="63"/>
-      <x:c r="D13" s="71" t="n">
+      <x:c r="B13" s="66"/>
+      <x:c r="C13" s="67"/>
+      <x:c r="D13" s="57" t="n">
         <x:f>SUM(D5:D12)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E13" s="61"/>
-      <x:c r="F13" s="62"/>
-      <x:c r="G13" s="63"/>
+      <x:c r="E13" s="65"/>
+      <x:c r="F13" s="66"/>
+      <x:c r="G13" s="67"/>
     </x:row>
     <x:row r="14" ht="20.100000381469727" customHeight="1">
       <x:c r="A14" s="5"/>
